--- a/data/model_ledgers/kbo-tie-aware-elo.xlsx
+++ b/data/model_ledgers/kbo-tie-aware-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -751,19 +751,19 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>win</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0.0650</t>
+          <t>1.1300</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T09:53:25.994801Z</t>
+          <t>2026-08-13T12:23:58.321282Z</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr"/>
@@ -869,19 +869,19 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>-0.2083</t>
+          <t>-1.2500</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T09:53:31.723233Z</t>
+          <t>2026-08-13T12:23:58.330764Z</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr"/>
@@ -982,14 +982,18 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>settled</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.056730Z</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="inlineStr"/>
@@ -1093,19 +1097,19 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>win</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>-0.0240</t>
+          <t>1.2019</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T09:53:37.329479Z</t>
+          <t>2026-08-13T12:23:58.339072Z</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr"/>
@@ -1116,8 +1120,1148 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>80730f47bc3b4065</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ebfa6aa870cd59eddca38e6fee1790eb5950520e37e8bbc45a537d489f5a8d4f</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>77220</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.528176</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.07772554954954947</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:47.512902Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>1.2200</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.069218Z</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>d08ccef3583146e2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ebfa6aa870cd59eddca38e6fee1790eb5950520e37e8bbc45a537d489f5a8d4f</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77221</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.515911</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>-0.0549044506437768</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:48.053744Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>0.7874</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.080921Z</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>e836eb01ba124fba</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ebfa6aa870cd59eddca38e6fee1790eb5950520e37e8bbc45a537d489f5a8d4f</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77222</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.518728</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>-0.1411359455782314</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:48.609845Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>0.5155</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.091770Z</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>c013ee70fac34d37</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ebfa6aa870cd59eddca38e6fee1790eb5950520e37e8bbc45a537d489f5a8d4f</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.56116</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>-0.0586118631178707</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:49.153171Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>0.5882</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.102842Z</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>663dd39c522e458d</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ebfa6aa870cd59eddca38e6fee1790eb5950520e37e8bbc45a537d489f5a8d4f</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77224</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.582312</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.051795568075117426</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:37:49.647423Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.112332Z</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5538719b3ac74c79</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77220</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.528176</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.07772554954954947</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:34.898609Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>1.2200</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.122750Z</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>4cd0e8bfbb694ccc</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>77221</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.515911</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>-0.04356036563876653</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:35.524021Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>0.7874</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.132955Z</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>bda7c1259952447d</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77222</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.518728</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>-0.1411359455782314</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:35.996158Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>0.5155</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.146442Z</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>800058fdf1c0401e</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.56116</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>-0.06846962962962955</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.470286Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>0.5882</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.156229Z</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>de4c5839e607414e</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>d6bd4347a18020935ff6c3057f43f5d72f8c98014abe7e6e70a66b1eca44b337</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>77224</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.582312</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.051795568075117426</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.934402Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:12.167091Z</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ5"/>
+  <autoFilter ref="A1:AJ15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>